--- a/Report_test.xlsx
+++ b/Report_test.xlsx
@@ -1,113 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\WORKS\ThuTrang\webfashion-playwright-Javascript\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3FBFCA-5D59-4BC3-91C8-15300E7C81BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="2835" yWindow="3000" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="Trang tính1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
-  <si>
-    <t>Tổng số testcase</t>
-  </si>
-  <si>
-    <t>Số testcase Pass</t>
-  </si>
-  <si>
-    <t>Số testcase Fail</t>
-  </si>
-  <si>
-    <t>Thời gian thực thi test</t>
-  </si>
-  <si>
-    <t>43.6s</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Precondition</t>
-  </si>
-  <si>
-    <t>Testcase</t>
-  </si>
-  <si>
-    <t>Steps</t>
-  </si>
-  <si>
-    <t>Expect</t>
-  </si>
-  <si>
-    <t>Test sults</t>
-  </si>
-  <si>
-    <t>Chomium</t>
-  </si>
-  <si>
-    <t>Firefox</t>
-  </si>
-  <si>
-    <t>Webkid</t>
-  </si>
-  <si>
-    <t>Time run</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Test Case 1: Register User</t>
-  </si>
-  <si>
-    <t>9.1s</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>32.7s</t>
-  </si>
-  <si>
-    <t>10.6s</t>
-  </si>
-  <si>
-    <t>Test Case 2: Login User with correct email and password</t>
-  </si>
-  <si>
-    <t>12.7s</t>
-  </si>
-  <si>
-    <t>33.7s</t>
-  </si>
-  <si>
-    <t>12.5s</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -136,23 +64,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -477,188 +396,200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="21.375" customWidth="1"/>
-    <col min="3" max="3" width="47.5" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K11"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tổng số testcase</v>
       </c>
       <c r="B1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Số testcase Pass</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Số testcase Fail</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Thời gian thực thi test</v>
+      </c>
+      <c r="B4" t="str">
+        <v>66.0s</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Version</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Precondition</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Testcase</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Steps</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Expect</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Test sults</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="F7" t="str">
+        <v>Chomium</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Firefox</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Webkid</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="F8" t="str">
+        <v>Time run</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Time run</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Time run</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v>Test Case 3: Login User with incorrect email and password</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>0.2s</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H9" t="str">
+        <v>3.7s</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="J9" t="str">
+        <v>0.8s</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Test Case 1: Register User</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>19.2s</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H10" t="str">
+        <v>43.4s</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="J10" t="str">
+        <v>12.3s</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Test Case 2: Login User with correct email and password</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>22.0s</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="H11" t="str">
+        <v>42.8s</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="J11" t="str">
+        <v>12.1s</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Pass</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +606,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K16" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>